--- a/OMS.Web/App_Data/Files/20260604_82_生産計画差異リスト.xlsx
+++ b/OMS.Web/App_Data/Files/20260604_82_生産計画差異リスト.xlsx
@@ -6,8 +6,8 @@
     <x:workbookView firstSheet="0" activeTab="0"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="差異リスト-内示" sheetId="1" r:id="rId2"/>
-    <x:sheet name="差異リスト-確定納入指示" sheetId="2" r:id="rId3"/>
+    <x:sheet name="生産計画差異リスト-内示" sheetId="1" r:id="rId2"/>
+    <x:sheet name="生産計画差異リスト-確定納入指示" sheetId="2" r:id="rId3"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="125725"/>
